--- a/lessons/codex-ai-video-workshop/materials/reference-results/07-payroll/payroll-review.xlsx
+++ b/lessons/codex-ai-video-workshop/materials/reference-results/07-payroll/payroll-review.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payroll review" sheetId="1" r:id="R1cfaa9f7f9c34513"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payroll review" sheetId="1" r:id="R1de17a3c434c4e1c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -431,7 +431,7 @@
     </x:row>
     <x:row r="9">
       <x:c r="A9" t="str">
-        <x:v>Fictional exercise: supplied withholding only. P04 excluded; no payments approved.</x:v>
+        <x:v>Supplied withholding only. P04 excluded pending timesheet approval.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
